--- a/Behind/june 2026/STT Report JUNE 2026.xlsx
+++ b/Behind/june 2026/STT Report JUNE 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76114F2-B135-48C6-A740-B5FC3A09C778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F29D5-8F12-4B44-B0E5-B4758FCB0D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2629,22 +2629,22 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,11 +2656,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3041,44 +3041,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="114" t="s">
+      <c r="A1" s="115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="111" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="111" t="s">
+      <c r="C1" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="111" t="s">
+      <c r="F1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="114" t="s">
+      <c r="G1" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="111" t="s">
+      <c r="H1" s="116" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="114" t="s">
+      <c r="K1" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
       <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
@@ -3094,61 +3094,61 @@
       <c r="Y1" s="119"/>
       <c r="Z1" s="119"/>
       <c r="AA1" s="119"/>
-      <c r="AB1" s="115" t="s">
+      <c r="AB1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="115" t="s">
+      <c r="AC1" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="115" t="s">
+      <c r="AD1" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="115" t="s">
+      <c r="AE1" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="115" t="s">
+      <c r="AF1" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="115" t="s">
+      <c r="AG1" s="113" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="115" t="s">
+      <c r="AI1" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="115" t="s">
+      <c r="AJ1" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="115" t="s">
+      <c r="AK1" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="115" t="s">
+      <c r="AL1" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="115" t="s">
+      <c r="AM1" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="120" t="s">
+      <c r="AN1" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="120" t="s">
+      <c r="AO1" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="115" t="s">
+      <c r="AP1" s="113" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="111"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="116"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3204,23 +3204,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="116"/>
-      <c r="AG2" s="116"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
+      <c r="AE2" s="114"/>
+      <c r="AF2" s="114"/>
+      <c r="AG2" s="114"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="116"/>
-      <c r="AJ2" s="116"/>
-      <c r="AK2" s="116"/>
-      <c r="AL2" s="116"/>
-      <c r="AM2" s="116"/>
-      <c r="AN2" s="121"/>
-      <c r="AO2" s="121"/>
-      <c r="AP2" s="116"/>
+      <c r="AI2" s="114"/>
+      <c r="AJ2" s="114"/>
+      <c r="AK2" s="114"/>
+      <c r="AL2" s="114"/>
+      <c r="AM2" s="114"/>
+      <c r="AN2" s="112"/>
+      <c r="AO2" s="112"/>
+      <c r="AP2" s="114"/>
     </row>
     <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AP38" s="12"/>
     </row>
-    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" s="70">
         <v>46209</v>
       </c>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="AP39" s="12"/>
     </row>
-    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" s="70">
         <v>46209</v>
       </c>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AP40" s="12"/>
     </row>
-    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" s="70">
         <v>46209</v>
       </c>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AP44" s="12"/>
     </row>
-    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45" s="70">
         <v>46211</v>
       </c>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AP60" s="12"/>
     </row>
-    <row r="61" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" s="70">
         <v>46212</v>
       </c>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="AP61" s="12"/>
     </row>
-    <row r="62" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" s="70">
         <v>46212</v>
       </c>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AP76" s="12"/>
     </row>
-    <row r="77" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A77" s="70">
         <v>46183</v>
       </c>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="AP77" s="12"/>
     </row>
-    <row r="78" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A78" s="70">
         <v>46183</v>
       </c>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AP78" s="12"/>
     </row>
-    <row r="79" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A79" s="70">
         <v>46183</v>
       </c>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="AP91" s="12"/>
     </row>
-    <row r="92" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A92" s="70">
         <v>46184</v>
       </c>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="AP93" s="12"/>
     </row>
-    <row r="94" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A94" s="70">
         <v>46184</v>
       </c>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="AP94" s="12"/>
     </row>
-    <row r="95" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A95" s="70">
         <v>46184</v>
       </c>
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AP105" s="12"/>
     </row>
-    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A106" s="70">
         <v>46185</v>
       </c>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="AP114" s="12"/>
     </row>
-    <row r="115" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A115" s="70">
         <v>46186</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>68</v>
       </c>
       <c r="F115" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G115" s="75" t="s">
         <v>115</v>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="AP115" s="12"/>
     </row>
-    <row r="116" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A116" s="70">
         <v>46186</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>68</v>
       </c>
       <c r="F116" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G116" s="75" t="s">
         <v>115</v>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="AP116" s="12"/>
     </row>
-    <row r="117" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A117" s="70">
         <v>46186</v>
       </c>
@@ -18487,7 +18487,7 @@
         <v>68</v>
       </c>
       <c r="F117" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G117" s="75" t="s">
         <v>115</v>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="AP117" s="12"/>
     </row>
-    <row r="118" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A118" s="70">
         <v>46186</v>
       </c>
@@ -18621,7 +18621,7 @@
         <v>68</v>
       </c>
       <c r="F118" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G118" s="75" t="s">
         <v>115</v>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="AP118" s="12"/>
     </row>
-    <row r="119" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A119" s="70">
         <v>46186</v>
       </c>
@@ -18755,7 +18755,7 @@
         <v>68</v>
       </c>
       <c r="F119" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G119" s="75" t="s">
         <v>115</v>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="AP119" s="12"/>
     </row>
-    <row r="120" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A120" s="70">
         <v>46186</v>
       </c>
@@ -18889,7 +18889,7 @@
         <v>68</v>
       </c>
       <c r="F120" s="72" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="G120" s="75" t="s">
         <v>115</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="AP131" s="12"/>
     </row>
-    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" s="70">
         <v>46189</v>
       </c>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="AP132" s="12"/>
     </row>
-    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" s="70">
         <v>46189</v>
       </c>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="AP133" s="12"/>
     </row>
-    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" s="70">
         <v>46189</v>
       </c>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AP134" s="12"/>
     </row>
-    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" s="70">
         <v>46189</v>
       </c>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AP135" s="12"/>
     </row>
-    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" s="70">
         <v>46189</v>
       </c>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="AP136" s="12"/>
     </row>
-    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" s="70">
         <v>46189</v>
       </c>
@@ -24350,7 +24350,7 @@
       </c>
       <c r="AP160" s="12"/>
     </row>
-    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A161" s="70">
         <v>46190</v>
       </c>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="AP161" s="12"/>
     </row>
-    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A162" s="70">
         <v>46190</v>
       </c>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="AP162" s="12"/>
     </row>
-    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A163" s="70">
         <v>46190</v>
       </c>
@@ -24746,7 +24746,7 @@
       </c>
       <c r="AP163" s="12"/>
     </row>
-    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A164" s="70">
         <v>46190</v>
       </c>
@@ -24878,7 +24878,7 @@
       </c>
       <c r="AP164" s="12"/>
     </row>
-    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A165" s="70">
         <v>46190</v>
       </c>
@@ -25010,7 +25010,7 @@
       </c>
       <c r="AP165" s="12"/>
     </row>
-    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A166" s="70">
         <v>46190</v>
       </c>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="AP166" s="12"/>
     </row>
-    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A167" s="70">
         <v>46190</v>
       </c>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="AP167" s="12"/>
     </row>
-    <row r="168" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A168" s="70">
         <v>46190</v>
       </c>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="AP168" s="12"/>
     </row>
-    <row r="169" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A169" s="70">
         <v>46190</v>
       </c>
@@ -25538,7 +25538,7 @@
       </c>
       <c r="AP169" s="12"/>
     </row>
-    <row r="170" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A170" s="70">
         <v>46190</v>
       </c>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="AP170" s="12"/>
     </row>
-    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A171" s="70">
         <v>46190</v>
       </c>
@@ -25802,7 +25802,7 @@
       </c>
       <c r="AP171" s="12"/>
     </row>
-    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A172" s="70">
         <v>46190</v>
       </c>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AP172" s="12"/>
     </row>
-    <row r="173" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A173" s="70">
         <v>46190</v>
       </c>
@@ -26066,7 +26066,7 @@
       </c>
       <c r="AP173" s="12"/>
     </row>
-    <row r="174" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A174" s="70">
         <v>46190</v>
       </c>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="AP174" s="12"/>
     </row>
-    <row r="175" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A175" s="70">
         <v>46190</v>
       </c>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AP175" s="12"/>
     </row>
-    <row r="176" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A176" s="70">
         <v>46190</v>
       </c>
@@ -27802,7 +27802,7 @@
       </c>
       <c r="AP186" s="12"/>
     </row>
-    <row r="187" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A187" s="70">
         <v>46191</v>
       </c>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="AP187" s="12"/>
     </row>
-    <row r="188" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A188" s="70">
         <v>46191</v>
       </c>
@@ -28066,7 +28066,7 @@
       </c>
       <c r="AP188" s="12"/>
     </row>
-    <row r="189" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A189" s="70">
         <v>46191</v>
       </c>
@@ -28198,7 +28198,7 @@
       </c>
       <c r="AP189" s="12"/>
     </row>
-    <row r="190" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A190" s="70">
         <v>46191</v>
       </c>
@@ -28330,7 +28330,7 @@
       </c>
       <c r="AP190" s="12"/>
     </row>
-    <row r="191" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A191" s="70">
         <v>46191</v>
       </c>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="AP191" s="12"/>
     </row>
-    <row r="192" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A192" s="70">
         <v>46191</v>
       </c>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AP192" s="12"/>
     </row>
-    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A193" s="70">
         <v>46191</v>
       </c>
@@ -28726,7 +28726,7 @@
       </c>
       <c r="AP193" s="12"/>
     </row>
-    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A194" s="70">
         <v>46191</v>
       </c>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="AP194" s="12"/>
     </row>
-    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A195" s="70">
         <v>46191</v>
       </c>
@@ -28990,7 +28990,7 @@
       </c>
       <c r="AP195" s="12"/>
     </row>
-    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A196" s="70">
         <v>46191</v>
       </c>
@@ -29122,7 +29122,7 @@
       </c>
       <c r="AP196" s="12"/>
     </row>
-    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A197" s="70">
         <v>46191</v>
       </c>
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AP197" s="12"/>
     </row>
-    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A198" s="70">
         <v>46191</v>
       </c>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="AP198" s="12"/>
     </row>
-    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A199" s="70">
         <v>46191</v>
       </c>
@@ -29518,7 +29518,7 @@
       </c>
       <c r="AP199" s="12"/>
     </row>
-    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A200" s="70">
         <v>46191</v>
       </c>
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AP200" s="12"/>
     </row>
-    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A201" s="70">
         <v>46191</v>
       </c>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="AP201" s="12"/>
     </row>
-    <row r="202" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A202" s="70">
         <v>46191</v>
       </c>
@@ -29914,7 +29914,7 @@
       </c>
       <c r="AP202" s="12"/>
     </row>
-    <row r="203" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A203" s="70">
         <v>46191</v>
       </c>
@@ -30046,7 +30046,7 @@
       </c>
       <c r="AP203" s="12"/>
     </row>
-    <row r="204" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A204" s="70">
         <v>46191</v>
       </c>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="AP204" s="12"/>
     </row>
-    <row r="205" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A205" s="70">
         <v>46191</v>
       </c>
@@ -31368,7 +31368,7 @@
       </c>
       <c r="AP213" s="12"/>
     </row>
-    <row r="214" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A214" s="70">
         <v>46192</v>
       </c>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="AP214" s="12"/>
     </row>
-    <row r="215" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A215" s="70">
         <v>46192</v>
       </c>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AP215" s="12"/>
     </row>
-    <row r="216" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A216" s="70">
         <v>46192</v>
       </c>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="AP216" s="12"/>
     </row>
-    <row r="217" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A217" s="70">
         <v>46192</v>
       </c>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="AP217" s="12"/>
     </row>
-    <row r="218" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A218" s="70">
         <v>46192</v>
       </c>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="AP218" s="12"/>
     </row>
-    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A219" s="70">
         <v>46192</v>
       </c>
@@ -32160,7 +32160,7 @@
       </c>
       <c r="AP219" s="12"/>
     </row>
-    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A220" s="70">
         <v>46192</v>
       </c>
@@ -32292,7 +32292,7 @@
       </c>
       <c r="AP220" s="12"/>
     </row>
-    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A221" s="70">
         <v>46192</v>
       </c>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="AP221" s="12"/>
     </row>
-    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A222" s="70">
         <v>46192</v>
       </c>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="AP222" s="12"/>
     </row>
-    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A223" s="70">
         <v>46192</v>
       </c>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="AP223" s="12"/>
     </row>
-    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A224" s="70">
         <v>46192</v>
       </c>
@@ -32820,7 +32820,7 @@
       </c>
       <c r="AP224" s="12"/>
     </row>
-    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A225" s="70">
         <v>46192</v>
       </c>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="AP225" s="12"/>
     </row>
-    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A226" s="70">
         <v>46192</v>
       </c>
@@ -33084,7 +33084,7 @@
       </c>
       <c r="AP226" s="12"/>
     </row>
-    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A227" s="70">
         <v>46192</v>
       </c>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="AP227" s="12"/>
     </row>
-    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A228" s="70">
         <v>46192</v>
       </c>
@@ -36162,7 +36162,7 @@
       </c>
       <c r="AP249" s="12"/>
     </row>
-    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A250" s="70">
         <v>46193</v>
       </c>
@@ -36294,7 +36294,7 @@
       </c>
       <c r="AP250" s="12"/>
     </row>
-    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A251" s="70">
         <v>46193</v>
       </c>
@@ -36682,7 +36682,7 @@
       </c>
       <c r="AP253" s="12"/>
     </row>
-    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A254" s="70">
         <v>46195</v>
       </c>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="AP318" s="12"/>
     </row>
-    <row r="319" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A319" s="70">
         <v>46196</v>
       </c>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="AP319" s="12"/>
     </row>
-    <row r="320" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A320" s="70">
         <v>46196</v>
       </c>
@@ -45160,7 +45160,7 @@
       </c>
       <c r="AP320" s="12"/>
     </row>
-    <row r="321" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A321" s="70">
         <v>46196</v>
       </c>
@@ -45290,7 +45290,7 @@
       </c>
       <c r="AP321" s="12"/>
     </row>
-    <row r="322" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A322" s="70">
         <v>46196</v>
       </c>
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AP322" s="12"/>
     </row>
-    <row r="323" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A323" s="70">
         <v>46196</v>
       </c>
@@ -45550,7 +45550,7 @@
       </c>
       <c r="AP323" s="12"/>
     </row>
-    <row r="324" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A324" s="70">
         <v>46196</v>
       </c>
@@ -45680,7 +45680,7 @@
       </c>
       <c r="AP324" s="12"/>
     </row>
-    <row r="325" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A325" s="70">
         <v>46196</v>
       </c>
@@ -45810,7 +45810,7 @@
       </c>
       <c r="AP325" s="12"/>
     </row>
-    <row r="326" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A326" s="70">
         <v>46196</v>
       </c>
@@ -45940,7 +45940,7 @@
       </c>
       <c r="AP326" s="12"/>
     </row>
-    <row r="327" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A327" s="70">
         <v>46196</v>
       </c>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="AP327" s="12"/>
     </row>
-    <row r="328" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A328" s="70">
         <v>46196</v>
       </c>
@@ -46200,7 +46200,7 @@
       </c>
       <c r="AP328" s="12"/>
     </row>
-    <row r="329" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A329" s="70">
         <v>46196</v>
       </c>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="AP329" s="12"/>
     </row>
-    <row r="330" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A330" s="70">
         <v>46197</v>
       </c>
@@ -46462,7 +46462,7 @@
       </c>
       <c r="AP330" s="12"/>
     </row>
-    <row r="331" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A331" s="70">
         <v>46197</v>
       </c>
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AP331" s="12"/>
     </row>
-    <row r="332" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A332" s="70">
         <v>46197</v>
       </c>
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AP332" s="12"/>
     </row>
-    <row r="333" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A333" s="70">
         <v>46197</v>
       </c>
@@ -46848,7 +46848,7 @@
       </c>
       <c r="AP333" s="12"/>
     </row>
-    <row r="334" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A334" s="70">
         <v>46197</v>
       </c>
@@ -46978,7 +46978,7 @@
       </c>
       <c r="AP334" s="12"/>
     </row>
-    <row r="335" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A335" s="70">
         <v>46197</v>
       </c>
@@ -48902,7 +48902,7 @@
       </c>
       <c r="AP349" s="12"/>
     </row>
-    <row r="350" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A350" s="70">
         <v>46202</v>
       </c>
@@ -49032,7 +49032,7 @@
       </c>
       <c r="AP350" s="12"/>
     </row>
-    <row r="351" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A351" s="70">
         <v>46202</v>
       </c>
@@ -49162,7 +49162,7 @@
       </c>
       <c r="AP351" s="12"/>
     </row>
-    <row r="352" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A352" s="70">
         <v>46202</v>
       </c>
@@ -49282,7 +49282,7 @@
       </c>
       <c r="AP352" s="12"/>
     </row>
-    <row r="353" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A353" s="70">
         <v>46202</v>
       </c>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="AP353" s="12"/>
     </row>
-    <row r="354" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A354" s="70">
         <v>46202</v>
       </c>
@@ -49542,7 +49542,7 @@
       </c>
       <c r="AP354" s="12"/>
     </row>
-    <row r="355" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A355" s="70">
         <v>46202</v>
       </c>
@@ -49598,7 +49598,7 @@
         <v>120</v>
       </c>
       <c r="S355" s="18">
-        <f t="shared" ref="S355:S398" si="123">J355+K355+L355+M355+O355+P355+Q355</f>
+        <f t="shared" ref="S355:S405" si="123">J355+K355+L355+M355+O355+P355+Q355</f>
         <v>280</v>
       </c>
       <c r="T355" s="18">
@@ -49674,7 +49674,7 @@
       </c>
       <c r="AP355" s="12"/>
     </row>
-    <row r="356" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A356" s="70">
         <v>46202</v>
       </c>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="AP356" s="12"/>
     </row>
-    <row r="357" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A357" s="70">
         <v>46202</v>
       </c>
@@ -49938,7 +49938,7 @@
       </c>
       <c r="AP357" s="12"/>
     </row>
-    <row r="358" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A358" s="70">
         <v>46202</v>
       </c>
@@ -50070,7 +50070,7 @@
       </c>
       <c r="AP358" s="12"/>
     </row>
-    <row r="359" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A359" s="70">
         <v>46202</v>
       </c>
@@ -50202,7 +50202,7 @@
       </c>
       <c r="AP359" s="12"/>
     </row>
-    <row r="360" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A360" s="70">
         <v>46202</v>
       </c>
@@ -50334,7 +50334,7 @@
       </c>
       <c r="AP360" s="12"/>
     </row>
-    <row r="361" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A361" s="70">
         <v>46202</v>
       </c>
@@ -50464,7 +50464,7 @@
       </c>
       <c r="AP361" s="12"/>
     </row>
-    <row r="362" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A362" s="70">
         <v>46202</v>
       </c>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="AP362" s="12"/>
     </row>
-    <row r="363" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A363" s="70">
         <v>46202</v>
       </c>
@@ -50720,7 +50720,7 @@
       </c>
       <c r="AP363" s="12"/>
     </row>
-    <row r="364" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A364" s="70">
         <v>46202</v>
       </c>
@@ -54616,7 +54616,7 @@
       </c>
       <c r="AP394" s="12"/>
     </row>
-    <row r="395" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A395" s="70">
         <v>46203</v>
       </c>
@@ -54746,7 +54746,7 @@
       </c>
       <c r="AP395" s="12"/>
     </row>
-    <row r="396" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A396" s="70">
         <v>46203</v>
       </c>
@@ -54876,7 +54876,7 @@
       </c>
       <c r="AP396" s="12"/>
     </row>
-    <row r="397" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A397" s="70">
         <v>46203</v>
       </c>
@@ -55006,7 +55006,7 @@
       </c>
       <c r="AP397" s="12"/>
     </row>
-    <row r="398" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A398" s="70">
         <v>46203</v>
       </c>
@@ -55136,7 +55136,7 @@
       </c>
       <c r="AP398" s="12"/>
     </row>
-    <row r="399" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A399" s="70">
         <v>46203</v>
       </c>
@@ -55189,7 +55189,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S399" s="18"/>
+      <c r="S399" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T399" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55233,14 +55236,14 @@
       </c>
       <c r="AE399" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF399" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG399" s="10">
         <f t="shared" si="124"/>
-        <v>272.80500000000001</v>
+        <v>1217.125</v>
       </c>
       <c r="AH399" s="64">
         <f t="shared" si="136"/>
@@ -55248,22 +55251,22 @@
       </c>
       <c r="AI399" s="9">
         <f t="shared" si="137"/>
-        <v>3924.1950000000002</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ399" s="5">
         <v>0.18</v>
       </c>
       <c r="AK399" s="11">
         <f t="shared" si="138"/>
-        <v>706.35509999999999</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL399" s="9">
         <f t="shared" si="139"/>
-        <v>4630.5501000000004</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP399" s="12"/>
     </row>
-    <row r="400" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A400" s="70">
         <v>46203</v>
       </c>
@@ -55316,7 +55319,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S400" s="18"/>
+      <c r="S400" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T400" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55360,14 +55366,14 @@
       </c>
       <c r="AE400" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF400" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG400" s="10">
         <f t="shared" si="124"/>
-        <v>272.80500000000001</v>
+        <v>1217.125</v>
       </c>
       <c r="AH400" s="64">
         <f t="shared" si="136"/>
@@ -55375,22 +55381,22 @@
       </c>
       <c r="AI400" s="9">
         <f t="shared" si="137"/>
-        <v>3924.1950000000002</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ400" s="5">
         <v>0.18</v>
       </c>
       <c r="AK400" s="11">
         <f t="shared" si="138"/>
-        <v>706.35509999999999</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL400" s="9">
         <f t="shared" si="139"/>
-        <v>4630.5501000000004</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP400" s="12"/>
     </row>
-    <row r="401" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A401" s="70">
         <v>46203</v>
       </c>
@@ -55443,7 +55449,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S401" s="18"/>
+      <c r="S401" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T401" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55487,14 +55496,14 @@
       </c>
       <c r="AE401" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF401" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG401" s="10">
         <f t="shared" si="124"/>
-        <v>272.80500000000001</v>
+        <v>1217.125</v>
       </c>
       <c r="AH401" s="64">
         <f t="shared" si="136"/>
@@ -55502,22 +55511,22 @@
       </c>
       <c r="AI401" s="9">
         <f t="shared" si="137"/>
-        <v>3924.1950000000002</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ401" s="5">
         <v>0.18</v>
       </c>
       <c r="AK401" s="11">
         <f t="shared" si="138"/>
-        <v>706.35509999999999</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL401" s="9">
         <f t="shared" si="139"/>
-        <v>4630.5501000000004</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP401" s="12"/>
     </row>
-    <row r="402" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A402" s="70">
         <v>46203</v>
       </c>
@@ -55570,7 +55579,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S402" s="18"/>
+      <c r="S402" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T402" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55614,14 +55626,14 @@
       </c>
       <c r="AE402" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF402" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG402" s="10">
         <f t="shared" si="124"/>
-        <v>272.80500000000001</v>
+        <v>1217.125</v>
       </c>
       <c r="AH402" s="64">
         <f t="shared" si="136"/>
@@ -55629,22 +55641,22 @@
       </c>
       <c r="AI402" s="9">
         <f t="shared" si="137"/>
-        <v>3924.1950000000002</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ402" s="5">
         <v>0.18</v>
       </c>
       <c r="AK402" s="11">
         <f t="shared" si="138"/>
-        <v>706.35509999999999</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL402" s="9">
         <f t="shared" si="139"/>
-        <v>4630.5501000000004</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP402" s="12"/>
     </row>
-    <row r="403" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A403" s="70">
         <v>46203</v>
       </c>
@@ -55697,7 +55709,10 @@
         <f t="shared" si="125"/>
         <v>240</v>
       </c>
-      <c r="S403" s="18"/>
+      <c r="S403" s="18">
+        <f t="shared" si="123"/>
+        <v>400</v>
+      </c>
       <c r="T403" s="18">
         <f t="shared" si="127"/>
         <v>4</v>
@@ -55741,14 +55756,14 @@
       </c>
       <c r="AE403" s="9">
         <f t="shared" si="135"/>
-        <v>8394</v>
+        <v>37450</v>
       </c>
       <c r="AF403" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG403" s="10">
         <f t="shared" si="124"/>
-        <v>545.61</v>
+        <v>2434.25</v>
       </c>
       <c r="AH403" s="64">
         <f t="shared" si="136"/>
@@ -55756,22 +55771,22 @@
       </c>
       <c r="AI403" s="9">
         <f t="shared" si="137"/>
-        <v>7848.39</v>
+        <v>35015.75</v>
       </c>
       <c r="AJ403" s="5">
         <v>0.18</v>
       </c>
       <c r="AK403" s="11">
         <f t="shared" si="138"/>
-        <v>1412.7102</v>
+        <v>6302.835</v>
       </c>
       <c r="AL403" s="9">
         <f t="shared" si="139"/>
-        <v>9261.1002000000008</v>
+        <v>41318.584999999999</v>
       </c>
       <c r="AP403" s="12"/>
     </row>
-    <row r="404" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A404" s="70">
         <v>46203</v>
       </c>
@@ -55824,7 +55839,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S404" s="18"/>
+      <c r="S404" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T404" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55868,14 +55886,14 @@
       </c>
       <c r="AE404" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF404" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG404" s="10">
         <f t="shared" si="124"/>
-        <v>272.80500000000001</v>
+        <v>1217.125</v>
       </c>
       <c r="AH404" s="64">
         <f t="shared" si="136"/>
@@ -55883,22 +55901,22 @@
       </c>
       <c r="AI404" s="9">
         <f t="shared" si="137"/>
-        <v>3924.1950000000002</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ404" s="5">
         <v>0.18</v>
       </c>
       <c r="AK404" s="11">
         <f t="shared" si="138"/>
-        <v>706.35509999999999</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL404" s="9">
         <f t="shared" si="139"/>
-        <v>4630.5501000000004</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP404" s="12"/>
     </row>
-    <row r="405" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A405" s="70">
         <v>46203</v>
       </c>
@@ -55951,7 +55969,10 @@
         <f t="shared" si="125"/>
         <v>120</v>
       </c>
-      <c r="S405" s="18"/>
+      <c r="S405" s="18">
+        <f t="shared" si="123"/>
+        <v>200</v>
+      </c>
       <c r="T405" s="18">
         <f t="shared" si="127"/>
         <v>2</v>
@@ -55995,14 +56016,14 @@
       </c>
       <c r="AE405" s="9">
         <f t="shared" si="135"/>
-        <v>4197</v>
+        <v>18725</v>
       </c>
       <c r="AF405" s="21">
         <v>0.1</v>
       </c>
       <c r="AG405" s="10">
         <f t="shared" si="124"/>
-        <v>419.70000000000005</v>
+        <v>1872.5</v>
       </c>
       <c r="AH405" s="64">
         <f t="shared" si="136"/>
@@ -56010,18 +56031,18 @@
       </c>
       <c r="AI405" s="9">
         <f t="shared" si="137"/>
-        <v>3777.3</v>
+        <v>16852.5</v>
       </c>
       <c r="AJ405" s="5">
         <v>0.18</v>
       </c>
       <c r="AK405" s="11">
         <f t="shared" si="138"/>
-        <v>679.91399999999999</v>
+        <v>3033.45</v>
       </c>
       <c r="AL405" s="9">
         <f t="shared" si="139"/>
-        <v>4457.2139999999999</v>
+        <v>19885.95</v>
       </c>
       <c r="AP405" s="12"/>
     </row>
@@ -57914,7 +57935,7 @@
       </c>
       <c r="S425" s="6">
         <f>SUM(S3:S424)</f>
-        <v>137113</v>
+        <v>138713</v>
       </c>
       <c r="T425" s="6">
         <f t="shared" si="141"/>
@@ -57953,12 +57974,12 @@
       <c r="AD425" s="6"/>
       <c r="AE425" s="6">
         <f>SUM(AE3:AE424)</f>
-        <v>12866067.894999988</v>
+        <v>12982291.894999988</v>
       </c>
       <c r="AF425" s="7"/>
       <c r="AG425" s="6">
         <f>SUM(AG3:AG424)</f>
-        <v>904591.03826250113</v>
+        <v>912654.07826250093</v>
       </c>
       <c r="AH425" s="6">
         <f>SUM(AH3:AH424)</f>
@@ -57966,15 +57987,15 @@
       </c>
       <c r="AI425" s="6">
         <f>SUM(AI3:AI424)</f>
-        <v>11961408.134237504</v>
+        <v>12069569.094237501</v>
       </c>
       <c r="AK425" s="6">
         <f>SUM(AK3:AK424)</f>
-        <v>2153053.4641627488</v>
+        <v>2172522.4369627498</v>
       </c>
       <c r="AL425" s="6">
         <f>SUM(AL3:AL424)</f>
-        <v>14114461.59840025</v>
+        <v>14242091.531200251</v>
       </c>
       <c r="AP425" s="12"/>
     </row>
@@ -58091,7 +58112,7 @@
       </c>
       <c r="S429" s="79">
         <f t="shared" si="142"/>
-        <v>3427.8249999999998</v>
+        <v>3467.8249999999998</v>
       </c>
       <c r="T429" s="79">
         <f t="shared" si="142"/>
@@ -58136,7 +58157,7 @@
       </c>
       <c r="AE429" s="57">
         <f t="shared" si="142"/>
-        <v>321651.6973749997</v>
+        <v>324557.29737499973</v>
       </c>
       <c r="AF429" s="57">
         <f t="shared" si="142"/>
@@ -58174,7 +58195,7 @@
       </c>
       <c r="S431" s="78">
         <f>S429+W429+AA429</f>
-        <v>3588.5224999999996</v>
+        <v>3628.5224999999996</v>
       </c>
       <c r="X431" t="s">
         <v>50</v>
@@ -58182,15 +58203,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP425" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
-    <filterColumn colId="5">
+    <filterColumn colId="7">
       <filters>
-        <filter val="LMT"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Al Fatah"/>
-        <filter val="Al-Fatah"/>
+        <filter val="Shakoor"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10" showButton="0"/>
@@ -58207,14 +58222,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58227,13 +58241,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
